--- a/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/02_Doküman, Kayıt ve Kaynak Kontrolü/EKG-YNT-LST-04_dis_kaynakli_dokuman_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/00_Yönetim Sistemi Çerçevesi/02_Doküman, Kayıt ve Kaynak Kontrolü/EKG-YNT-LST-04_dis_kaynakli_dokuman_listesi.xlsx
@@ -1085,7 +1085,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-LST-04&amp;C&amp;"Arial,Regular"&amp;11Dış Kaynaklı Doküman Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 08.06.2026 | Revizyon: 14.09.2026
+Revizyon nedeni: Dış kaynak takibi güncel sürüm, kapsam, yetkili kaynak ve değişiklik etkisini izleyen sekiz sütuna indirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>